--- a/docs/gerenciamento/Informacoes_Finais_Projeto_Integrantes_v1.xlsx
+++ b/docs/gerenciamento/Informacoes_Finais_Projeto_Integrantes_v1.xlsx
@@ -1,105 +1,178 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Gabri\Downloads\Healthcare Data Analytics Dashboard\docs\gerenciamento\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87C5FB82-7ABD-4803-B766-626D729C4265}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dados_Finais_Proj_Integrantes" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Exemplo_Prrenchimento" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Dados_Finais_Proj_Integrantes" sheetId="1" r:id="rId1"/>
+    <sheet name="Exemplo_Prrenchimento" sheetId="2" r:id="rId2"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="191028" fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="21">
+  <si>
+    <t>DADOS FINAIS E OFICIAIS DO PROJETO DO CHALLENGE 2026</t>
+  </si>
+  <si>
+    <t>NOME DA EQUIPE:</t>
+  </si>
+  <si>
+    <t>GRUPO 61</t>
+  </si>
+  <si>
+    <t>NOME DO PROJETO:</t>
+  </si>
+  <si>
+    <t>LEITO360</t>
+  </si>
+  <si>
+    <t>DESCRIÇÃO RESUMIDA DO PROJETO:</t>
+  </si>
+  <si>
+    <t>O LEITO360 é uma plataforma analítica que integra dados públicos do SIH/SUS, CNES e IBGE no Oracle AI Database, utilizando dados relacionais, JSON e CSV, com Select AI para consultas em linguagem natural e dashboard web para análise de internações, permanência, mortalidade e capacidade cadastrada de leitos SUS.</t>
+  </si>
+  <si>
+    <t>RM</t>
+  </si>
+  <si>
+    <t>NOME DO COMPONENTE EM ORDEM ALFABÉTICA</t>
+  </si>
+  <si>
+    <t>GABRIEL SILVA DE JESUS (representante)</t>
+  </si>
+  <si>
+    <t>JOÃO GABRIEL BERNARDES</t>
+  </si>
+  <si>
+    <t>NATÁLIA NAOMI NAKAMURA</t>
+  </si>
+  <si>
+    <t>PEDRO HENRIQUE WEI CHERN</t>
+  </si>
+  <si>
+    <t>VITÓRIA CRISTINA DA SILVA COUTINHO</t>
+  </si>
+  <si>
+    <t>Desbravadores da IA</t>
+  </si>
+  <si>
+    <t>IA GENERATION</t>
+  </si>
+  <si>
+    <t>ESSE PROJETO TEM POR OBJETIVO ATENDER AOS CLIENTES DE FORMA AUTOMÁTICA E SEM INTERRUPÇÃO, AUTOMATIZAR TODAS AS TAREFAS ATÉ A CONCLUSÃO DO ATENDIMENTO, SEM INTERVENÇÃO HUMANA.</t>
+  </si>
+  <si>
+    <t>BEATRIZ ALVARES JÚLIO</t>
+  </si>
+  <si>
+    <t>MARIA JÚLIA TAVARES</t>
+  </si>
+  <si>
+    <t>SILVANA SAKSPILDAP (representante)</t>
+  </si>
+  <si>
+    <t>TEREZA LIMA CORDEIRO</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="9">
-    <font>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="9" x14ac:knownFonts="1">
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
       <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
+      <color theme="1"/>
       <name val="Arial"/>
       <family val="2"/>
-      <b val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="16"/>
       <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FF0070C0"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
       <sz val="11"/>
-    </font>
-    <font>
+      <color rgb="FF0070C0"/>
       <name val="Arial"/>
       <family val="2"/>
-      <color theme="1"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
-    </font>
-    <font>
+      <color rgb="FF0070C0"/>
       <name val="Arial"/>
       <family val="2"/>
-      <b val="1"/>
-      <color theme="1"/>
-      <sz val="16"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <family val="2"/>
-      <b val="1"/>
-      <color theme="1"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <family val="2"/>
-      <color theme="1"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <family val="2"/>
-      <b val="1"/>
-      <color rgb="FF0070C0"/>
-      <sz val="12"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <family val="2"/>
-      <color rgb="FF0070C0"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <family val="2"/>
-      <b val="1"/>
-      <color rgb="FF0070C0"/>
-      <sz val="11"/>
     </font>
   </fonts>
   <fills count="4">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.7999816888943144"/>
+        <fgColor theme="8" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.5999938962981048"/>
+        <fgColor theme="8" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="8">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -141,173 +214,75 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
       <top style="thin">
         <color indexed="64"/>
       </top>
       <bottom style="thin">
         <color indexed="64"/>
       </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
       <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+  <cellXfs count="16">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -607,267 +582,205 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="B2:C13"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.45"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="B1:C13"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col width="1.42578125" customWidth="1" min="1" max="1"/>
-    <col width="24" customWidth="1" min="2" max="2"/>
-    <col width="84.28515625" customWidth="1" min="3" max="3"/>
+    <col min="1" max="1" width="1.42578125" customWidth="1"/>
+    <col min="2" max="2" width="24" customWidth="1"/>
+    <col min="3" max="3" width="84.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="7.15" customHeight="1"/>
-    <row r="2" ht="39" customHeight="1">
-      <c r="B2" s="16" t="inlineStr">
-        <is>
-          <t>DADOS FINAIS E OFICIAIS DO PROJETO DO CHALLENGE 2026</t>
-        </is>
-      </c>
-      <c r="C2" s="17" t="n"/>
-    </row>
-    <row r="3" ht="24.6" customHeight="1">
-      <c r="B3" s="7" t="inlineStr">
-        <is>
-          <t>NOME DA EQUIPE:</t>
-        </is>
-      </c>
-      <c r="C3" s="1" t="inlineStr">
-        <is>
-          <t>GRUPO 61</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="24.6" customHeight="1">
-      <c r="B4" s="7" t="inlineStr">
-        <is>
-          <t>NOME DO PROJETO:</t>
-        </is>
-      </c>
-      <c r="C4" s="1" t="inlineStr">
-        <is>
-          <t>LEITO360</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="3.6" customHeight="1">
-      <c r="B5" s="8" t="n"/>
-      <c r="C5" s="2" t="n"/>
-    </row>
-    <row r="6" ht="115.9" customHeight="1">
-      <c r="B6" s="9" t="inlineStr">
-        <is>
-          <t>DESCRIÇÃO RESUMIDA DO PROJETO:</t>
-        </is>
-      </c>
-      <c r="C6" s="3" t="inlineStr">
-        <is>
-          <t>O LEITO360 é uma plataforma analítica que integra dados públicos do SIH/SUS, CNES e IBGE no Oracle AI Database, utilizando dados relacionais, JSON e CSV, com Select AI para consultas em linguagem natural e dashboard web para análise de internações, permanência, mortalidade e capacidade cadastrada de leitos SUS.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="3.6" customHeight="1">
-      <c r="B7" s="4" t="n"/>
-      <c r="C7" s="5" t="n"/>
-    </row>
-    <row r="8" ht="24.6" customHeight="1">
-      <c r="B8" s="10" t="inlineStr">
-        <is>
-          <t>RM</t>
-        </is>
-      </c>
-      <c r="C8" s="7" t="inlineStr">
-        <is>
-          <t>NOME DO COMPONENTE EM ORDEM ALFABÉTICA</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="24.6" customHeight="1">
-      <c r="B9" s="6" t="n">
+    <row r="1" spans="2:3" ht="7.15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="2" spans="2:3" ht="39" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B2" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="15"/>
+    </row>
+    <row r="3" spans="2:3" ht="24.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B3" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="2:3" ht="24.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B4" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="2:3" ht="3.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B5" s="8"/>
+      <c r="C5" s="2"/>
+    </row>
+    <row r="6" spans="2:3" ht="115.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B6" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7" spans="2:3" ht="3.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B7" s="4"/>
+      <c r="C7" s="5"/>
+    </row>
+    <row r="8" spans="2:3" ht="24.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B8" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9" spans="2:3" ht="24.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B9" s="6">
         <v>569250</v>
       </c>
-      <c r="C9" s="6" t="inlineStr">
-        <is>
-          <t>GABRIEL SILVA DE JESUS (representante)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="24.6" customHeight="1">
-      <c r="B10" s="6" t="n">
+      <c r="C9" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="10" spans="2:3" ht="24.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B10" s="6">
         <v>573021</v>
       </c>
-      <c r="C10" s="6" t="inlineStr">
-        <is>
-          <t>JOÃO GABRIEL BERNARDES</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="24.6" customHeight="1">
-      <c r="B11" s="6" t="n">
+      <c r="C10" s="6" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11" spans="2:3" ht="24.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B11" s="6">
         <v>570993</v>
       </c>
-      <c r="C11" s="6" t="inlineStr">
-        <is>
-          <t>NATÁLIA NAOMI NAKAMURA</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="24.6" customHeight="1">
-      <c r="B12" s="6" t="n">
+      <c r="C11" s="6" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="12" spans="2:3" ht="24.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B12" s="6">
         <v>568816</v>
       </c>
-      <c r="C12" s="6" t="inlineStr">
-        <is>
-          <t>PEDRO HENRIQUE WEI CHERN</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="B13" t="n">
+      <c r="C12" s="6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="13" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B13" s="6">
         <v>570130</v>
       </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>VITÓRIA CRISTINA DA SILVA COUTINHO</t>
-        </is>
+      <c r="C13" s="6" t="s">
+        <v>13</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="B2:C2"/>
   </mergeCells>
-  <pageMargins left="0.511811024" right="0.511811024" top="0.787401575" bottom="0.787401575" header="0.31496062" footer="0.31496062"/>
-  <pageSetup orientation="portrait" paperSize="9"/>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="B2:C12"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.45"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="B1:C12"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col width="1.42578125" customWidth="1" min="1" max="1"/>
-    <col width="24" customWidth="1" min="2" max="2"/>
-    <col width="76.7109375" customWidth="1" min="3" max="3"/>
+    <col min="1" max="1" width="1.42578125" customWidth="1"/>
+    <col min="2" max="2" width="24" customWidth="1"/>
+    <col min="3" max="3" width="76.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="7.15" customHeight="1"/>
-    <row r="2" ht="39" customHeight="1">
-      <c r="B2" s="16" t="inlineStr">
-        <is>
-          <t>DADOS FINAIS E OFICIAIS DO PROJETO DO CHALLENGE 2026</t>
-        </is>
-      </c>
-      <c r="C2" s="17" t="n"/>
-    </row>
-    <row r="3" ht="24.6" customHeight="1">
-      <c r="B3" s="7" t="inlineStr">
-        <is>
-          <t>NOME DA EQUIPE:</t>
-        </is>
-      </c>
-      <c r="C3" s="11" t="inlineStr">
-        <is>
-          <t>Desbravadores da IA</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="24.6" customHeight="1">
-      <c r="B4" s="7" t="inlineStr">
-        <is>
-          <t>NOME DO PROJETO:</t>
-        </is>
-      </c>
-      <c r="C4" s="11" t="inlineStr">
-        <is>
-          <t>IA GENERATION</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="3.6" customHeight="1">
-      <c r="B5" s="8" t="n"/>
-      <c r="C5" s="2" t="n"/>
-    </row>
-    <row r="6" ht="115.9" customHeight="1">
-      <c r="B6" s="9" t="inlineStr">
-        <is>
-          <t>DESCRIÇÃO RESUMIDA DO PROJETO:</t>
-        </is>
-      </c>
-      <c r="C6" s="12" t="inlineStr">
-        <is>
-          <t>ESSE PROJETO TEM POR OBJETIVO ATENDER AOS CLIENTES DE FORMA AUTOMÁTICA E SEM INTERRUPÇÃO, AUTOMATIZAR TODAS AS TAREFAS ATÉ A CONCLUSÃO DO ATENDIMENTO, SEM INTERVENÇÃO HUMANA.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="3.6" customHeight="1">
-      <c r="B7" s="4" t="n"/>
-      <c r="C7" s="5" t="n"/>
-    </row>
-    <row r="8" ht="24.6" customHeight="1">
-      <c r="B8" s="10" t="inlineStr">
-        <is>
-          <t>RM</t>
-        </is>
-      </c>
-      <c r="C8" s="7" t="inlineStr">
-        <is>
-          <t>NOME DO COMPONENTE EM ORDEM ALFABÉTICA</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="24.6" customHeight="1">
-      <c r="B9" s="13" t="n">
+    <row r="1" spans="2:3" ht="7.15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="2" spans="2:3" ht="39" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B2" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="15"/>
+    </row>
+    <row r="3" spans="2:3" ht="24.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B3" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="11" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4" spans="2:3" ht="24.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B4" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C4" s="11" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="5" spans="2:3" ht="3.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B5" s="8"/>
+      <c r="C5" s="2"/>
+    </row>
+    <row r="6" spans="2:3" ht="115.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B6" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="C6" s="12" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="7" spans="2:3" ht="3.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B7" s="4"/>
+      <c r="C7" s="5"/>
+    </row>
+    <row r="8" spans="2:3" ht="24.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B8" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9" spans="2:3" ht="24.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B9" s="13">
         <v>789231</v>
       </c>
-      <c r="C9" s="13" t="inlineStr">
-        <is>
-          <t>BEATRIZ ALVARES JÚLIO</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="24.6" customHeight="1">
-      <c r="B10" s="13" t="n">
+      <c r="C9" s="13" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="10" spans="2:3" ht="24.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B10" s="13">
         <v>789489</v>
       </c>
-      <c r="C10" s="13" t="inlineStr">
-        <is>
-          <t>MARIA JÚLIA TAVARES</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="24.6" customHeight="1">
-      <c r="B11" s="13" t="n">
+      <c r="C10" s="13" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="11" spans="2:3" ht="24.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B11" s="13">
         <v>789231</v>
       </c>
-      <c r="C11" s="13" t="inlineStr">
-        <is>
-          <t>SILVANA SAKSPILDAP (representante)</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="24.6" customHeight="1">
-      <c r="B12" s="13" t="n">
+      <c r="C11" s="13" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="12" spans="2:3" ht="24.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B12" s="13">
         <v>789453</v>
       </c>
-      <c r="C12" s="13" t="inlineStr">
-        <is>
-          <t>TEREZA LIMA CORDEIRO</t>
-        </is>
+      <c r="C12" s="13" t="s">
+        <v>20</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="B2:C2"/>
   </mergeCells>
-  <pageMargins left="0.511811024" right="0.511811024" top="0.787401575" bottom="0.787401575" header="0.31496062" footer="0.31496062"/>
-  <pageSetup orientation="portrait" paperSize="9"/>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
 </file>